--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5745,7 +5745,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>184</v>
       </c>
@@ -5760,13 +5760,13 @@
         <v>62</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5848,7 +5848,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>188</v>
       </c>
@@ -5863,13 +5863,13 @@
         <v>189</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>74</v>
@@ -6157,7 +6157,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>202</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3381" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3381" uniqueCount="348">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -851,6 +851,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -7985,7 +7989,7 @@
         <v>74</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>74</v>
+        <v>273</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>74</v>
@@ -7993,10 +7997,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8022,10 +8026,10 @@
         <v>91</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8056,7 +8060,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -8074,7 +8078,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8094,10 +8098,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8195,10 +8199,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8239,7 +8243,7 @@
         <v>74</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>74</v>
@@ -8298,10 +8302,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8401,10 +8405,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8504,10 +8508,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8607,10 +8611,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8710,10 +8714,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8811,10 +8815,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8912,10 +8916,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9015,10 +9019,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9118,10 +9122,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9221,10 +9225,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9247,7 +9251,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9300,7 +9304,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9320,10 +9324,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9346,7 +9350,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9379,7 +9383,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9397,7 +9401,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9417,10 +9421,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9443,7 +9447,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9496,7 +9500,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9516,10 +9520,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9575,25 +9579,25 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9613,10 +9617,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9639,13 +9643,13 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9676,7 +9680,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>74</v>
@@ -9694,7 +9698,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9714,10 +9718,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9740,7 +9744,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9773,25 +9777,25 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9811,10 +9815,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9837,7 +9841,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9870,25 +9874,25 @@
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9908,10 +9912,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9938,7 +9942,7 @@
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9989,7 +9993,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10009,10 +10013,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10035,7 +10039,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10088,7 +10092,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10108,10 +10112,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10134,7 +10138,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10187,7 +10191,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10207,10 +10211,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10233,7 +10237,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10286,7 +10290,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10306,10 +10310,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10332,7 +10336,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10385,7 +10389,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10405,10 +10409,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10431,7 +10435,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10484,7 +10488,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10504,10 +10508,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10530,7 +10534,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10583,7 +10587,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10603,10 +10607,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10629,7 +10633,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10682,7 +10686,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10702,10 +10706,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10728,7 +10732,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10781,7 +10785,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10801,10 +10805,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10827,7 +10831,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10880,7 +10884,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10900,10 +10904,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10926,7 +10930,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10979,7 +10983,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -10999,10 +11003,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11025,11 +11029,11 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11080,7 +11084,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11100,10 +11104,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11201,10 +11205,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11302,10 +11306,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11403,10 +11407,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11504,10 +11508,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11607,10 +11611,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11710,10 +11714,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11813,10 +11817,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11916,10 +11920,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12017,10 +12021,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12054,7 +12058,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>74</v>
@@ -12076,7 +12080,7 @@
       </c>
       <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>74</v>
@@ -12094,7 +12098,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12114,10 +12118,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12140,7 +12144,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12193,7 +12197,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -12213,10 +12217,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12239,7 +12243,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12292,7 +12296,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-du-probleme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
